--- a/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Camille s'assoit à la table de la cuisine. Papa a un calendrier en carton. Il y a sept cases. Papa dit : il y a sept jours. Camille touche le carton. C'est un peu rêche. Papa pose un jeton. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Papa dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Camille répète les sept jours dans l'ordre. Parce qu'elle les dit dans l'ordre, elle se souvient. Papa avance le jeton. Camille dit : après lundi, c'est mardi. Papa sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. Camille pose le jeton sur mercredi. Elle sent le bois du jeton. Papa dit : encore. Camille dit toute la liste. Lundi commence. Dimanche termine.</t>
+          <t>Camille s'assoit à la table de la cuisine. Papa a un calendrier en carton. Il y a sept cases. Il y a sept jours. Camille touche le carton. C'est un peu rêche. Papa pose un jeton. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Camille répète les sept jours dans l'ordre. Parce qu'elle les dit dans l'ordre, elle se souvient. Papa avance le jeton. Après lundi, c'est mardi. Papa sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. Camille pose le jeton sur mercredi. Elle sent le bois du jeton. Encore. Camille dit toute la liste. Lundi commence. Dimanche termine.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Camille s'assoit à la table de la cuisine. Papa a un calendrier en carton. Il y a sept cases.
+papa|Il y a sept jours.
+narrateur|Camille touche le carton. C'est un peu rêche. Papa pose un jeton. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes.
+papa|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
+narrateur|Camille répète les sept jours dans l'ordre. Parce qu'elle les dit dans l'ordre, elle se souvient. Papa avance le jeton.
+enfant-f|Après lundi, c'est mardi. Papa sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre.
+narrateur|Camille pose le jeton sur mercredi. Elle sent le bois du jeton.
+papa|Encore.
+narrateur|Camille dit toute la liste. Lundi commence. Dimanche termine.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Camille a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Camille pose le jeton sur lundi. Papa range le calendrier.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,11 @@
 narrateur|Camille dit toute la liste. Lundi commence. Dimanche termine.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Camille a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Camille pose le jeton sur lundi. Papa range le calendrier.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camille et les sept jours</t>
+          <t>Le livre et le pain</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut un livre de bateau. Mercredi à la bibliothèque, le livre est trop haut. Papa l'aide à le montrer. Jeudi, le pain chaud. Elle ouvre le livre, des miettes tombent sur la voile.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Camille s'assoit à la table de la cuisine. Papa a un calendrier en carton. Il y a sept cases. Il y a sept jours. Camille touche le carton. C'est un peu rêche. Papa pose un jeton. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Camille répète les sept jours dans l'ordre. Parce qu'elle les dit dans l'ordre, elle se souvient. Papa avance le jeton. Après lundi, c'est mardi. Papa sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. Camille pose le jeton sur mercredi. Elle sent le bois du jeton. Encore. Camille dit toute la liste. Lundi commence. Dimanche termine.</t>
+          <t>Un marque-page rouge dépasse du gros livre. La salle sent le papier et le bois ciré. Une chaise racle tout doux. La lumière tombe en carré sur le tapis. Tu as senti le papier, Nina ? Il sent le calme. C'est mercredi. Mercredi, c'est la bibliothèque. En ce moment, Nina cherche un bateau. Je veux le livre du bateau. Celui avec la voile bleue. On le cherche. Les dos des livres sont serrés. Nina passe le doigt sur les titres. Le doigt s'arrête trop bas. Il est tout en haut. Trop haut pour ta main. Nina pousse le tabouret. Le tabouret glisse, puis tient. Je montre lequel. Tu montes un pied. Je tiens le tabouret. Nina pointe le dos bleu. Papa le descend tout doux. La voile ! Tu l'as trouvé. Le livre est lourd, un peu froid. Je le lis avec du pain. Demain, c'est jeudi. Jeudi, on prend le pain. La semaine a sept jours. Quel jour vient après mercredi ? Jeudi. Oui. Nina serre le livre contre elle. Le marque-page rouge tape son poignet.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Camille s'assoit à la table de la cuisine. Papa a un calendrier en carton. Il y a &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; cases. Papa dit : il y a sept jours. Camille touche le carton. C'est un peu rêche. Papa pose un jeton. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Papa dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Camille répète les sept jours dans l'ordre. Parce qu'elle les dit dans l'ordre, elle se souvient. Papa avance le jeton. Camille dit : après lundi, c'est mardi. Papa sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. Camille pose le jeton sur mercredi. Elle sent le bois du jeton. Papa dit : encore. Camille dit toute la liste. Lundi commence. Dimanche termine.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un marque-page rouge dépasse du gros livre. La salle sent le papier et le bois ciré. Une chaise racle tout doux. La lumière tombe en carré sur le tapis. Tu as senti le papier, Nina ? Il sent le calme. C'est mercredi. Mercredi, c'est la bibliothèque. En ce moment, Nina cherche un bateau. Je veux le livre du bateau. Celui avec la voile bleue. On le cherche. Les dos des livres sont serrés. Nina passe le doigt sur les titres. Le doigt s'arrête trop bas. Il est tout en haut. Trop haut pour ta main. Nina pousse le tabouret. Le tabouret glisse, puis tient. Je montre lequel. Tu montes un pied. Je tiens le tabouret. Nina pointe le dos bleu. Papa le descend tout doux. La voile ! Tu l'as trouvé. Le livre est lourd, un peu froid. Je le lis avec du pain. Demain, c'est jeudi. Jeudi, on prend le pain. La semaine a sept jours. Quel jour vient après mercredi ? Jeudi. Oui. Nina serre le livre contre elle. Le marque-page rouge tape son poignet.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,42 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Camille s'assoit à la table de la cuisine. Papa a un calendrier en carton. Il y a sept cases.
-papa|Il y a sept jours.
-narrateur|Camille touche le carton. C'est un peu rêche. Papa pose un jeton. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes.
-papa|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
-narrateur|Camille répète les sept jours dans l'ordre. Parce qu'elle les dit dans l'ordre, elle se souvient. Papa avance le jeton.
-enfant-f|Après lundi, c'est mardi. Papa sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre.
-narrateur|Camille pose le jeton sur mercredi. Elle sent le bois du jeton.
-papa|Encore.
-narrateur|Camille dit toute la liste. Lundi commence. Dimanche termine.</t>
+          <t>narrateur|Un marque-page rouge dépasse du gros livre.
+narrateur|La salle sent le papier et le bois ciré.
+narrateur|Une chaise racle tout doux.
+narrateur|La lumière tombe en carré sur le tapis.
+papa|Tu as senti le papier, Nina ?
+enfant-f|Il sent le calme.
+papa|C'est mercredi.
+papa|Mercredi, c'est la bibliothèque.
+narrateur|En ce moment, Nina cherche un bateau.
+enfant-f|Je veux le livre du bateau.
+enfant-f|Celui avec la voile bleue.
+papa|On le cherche.
+narrateur|Les dos des livres sont serrés.
+narrateur|Nina passe le doigt sur les titres.
+narrateur|Le doigt s'arrête trop bas.
+enfant-f|Il est tout en haut.
+papa|Trop haut pour ta main.
+narrateur|Nina pousse le tabouret.
+narrateur|Le tabouret glisse, puis tient.
+enfant-f|Je montre lequel.
+papa|Tu montes un pied.
+papa|Je tiens le tabouret.
+narrateur|Nina pointe le dos bleu.
+narrateur|Papa le descend tout doux.
+enfant-f|La voile !
+papa|Tu l'as trouvé.
+narrateur|Le livre est lourd, un peu froid.
+enfant-f|Je le lis avec du pain.
+papa|Demain, c'est jeudi.
+papa|Jeudi, on prend le pain.
+papa|La semaine a sept jours.
+papa|Quel jour vient après mercredi ?
+enfant-f|Jeudi.
+papa|Oui.
+narrateur|Nina serre le livre contre elle.
+narrateur|Le marque-page rouge tape son poignet.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1352,12 +1391,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après lundi, quel jour vient ?</t>
+          <t>Après mercredi, quel jour vient ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après lundi, quel jour vient ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après mercredi, quel jour vient ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,12 +1406,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>mardi</t>
+          <t>jeudi</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>mardi | c'est mardi | le mardi</t>
+          <t>jeudi | le jeudi | c'est jeudi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1387,7 +1426,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Lundi, puis mardi. Quel jour après lundi ?</t>
+          <t>Mercredi, la bibliothèque. Quel jour vient après ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1436,7 +1475,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1547,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après lundi, quel jour vient ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Après mercredi, quel jour vient ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Camille a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
+          <t>Le lendemain, la rue sent le four. Une miche dorée brille derrière la vitre. C'est jeudi, Nina. Le jour du pain. Il est chaud ? On va le prendre. Nina tient encore le livre sous le bras. La couverture frotte son manteau. Papa prend la miche. Le papier craque. Je l'ouvre à la maison. Le livre ou le pain ? Les deux. Merci, Nina. Tu as attendu jeudi. La miche chauffe le creux du sac. Le livre reste contre Nina.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Camille a dit les &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre. Lundi commence. Dimanche termine.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lendemain, la rue sent le four. Une miche dorée brille derrière la vitre. C'est jeudi, Nina. Le jour du pain. Il est chaud ? On va le prendre. Nina tient encore le livre sous le bras. La couverture frotte son manteau. Papa prend la miche. Le papier craque. Je l'ouvre à la maison. Le livre ou le pain ? Les deux. Merci, Nina. Tu as attendu jeudi. La miche chauffe le creux du sac. Le livre reste contre Nina.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1604,7 +1642,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1718,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Camille a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lendemain, la rue sent le four.
+narrateur|Une miche dorée brille derrière la vitre.
+papa|C'est jeudi, Nina.
+papa|Le jour du pain.
+enfant-f|Il est chaud ?
+papa|On va le prendre.
+narrateur|Nina tient encore le livre sous le bras.
+narrateur|La couverture frotte son manteau.
+narrateur|Papa prend la miche.
+narrateur|Le papier craque.
+enfant-f|Je l'ouvre à la maison.
+papa|Le livre ou le pain ?
+enfant-f|Les deux.
+papa|Merci, Nina.
+papa|Tu as attendu jeudi.
+narrateur|La miche chauffe le creux du sac.
+narrateur|Le livre reste contre Nina.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1761,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Camille pose le jeton sur lundi. Papa range le calendrier.</t>
+          <t>La table de la cuisine est claire. Nina pose le livre. Tu tournes la page ? La voile bleue. Papa casse le pain. Une miette tombe sur la voile. Le bateau a du pain. On souffle. La miette part. Le papier sent le four, un peu. Mercredi, le livre. Jeudi, le pain. J'ai les deux. Oui. Nina mord un morceau de croûte. La croûte casse, tout net. Il est chaud. Comme tu voulais. Le marque-page rouge garde la page.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Camille pose le jeton sur lundi. Papa range le calendrier.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La table de la cuisine est claire. Nina pose le livre. Tu tournes la page ? La voile bleue. Papa casse le pain. Une miette tombe sur la voile. Le bateau a du pain. On souffle. La miette part. Le papier sent le four, un peu. Mercredi, le livre. Jeudi, le pain. J'ai les deux. Oui. Nina mord un morceau de croûte. La croûte casse, tout net. Il est chaud. Comme tu voulais. Le marque-page rouge garde la page.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1776,7 +1829,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1897,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Camille pose le jeton sur lundi. Papa range le calendrier.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La table de la cuisine est claire.
+narrateur|Nina pose le livre.
+papa|Tu tournes la page ?
+enfant-f|La voile bleue.
+narrateur|Papa casse le pain.
+narrateur|Une miette tombe sur la voile.
+enfant-f|Le bateau a du pain.
+papa|On souffle.
+narrateur|La miette part.
+narrateur|Le papier sent le four, un peu.
+papa|Mercredi, le livre.
+papa|Jeudi, le pain.
+enfant-f|J'ai les deux.
+papa|Oui.
+narrateur|Nina mord un morceau de croûte.
+narrateur|La croûte casse, tout net.
+enfant-f|Il est chaud.
+papa|Comme tu voulais.
+narrateur|Le marque-page rouge garde la page.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina pose la main à plat sur la voile. Le bateau est à moi. Oui. Le pain aussi. Une miette dore encore au creux de la page.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina pose la main à plat sur la voile. Le bateau est à moi. Oui. Le pain aussi. Une miette dore encore au creux de la page.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,14 +2003,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2012,10 +2082,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina pose la main à plat sur la voile.
+enfant-f|Le bateau est à moi.
+papa|Oui.
+papa|Le pain aussi.
+narrateur|Une miette dore encore au creux de la page.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>bibliothèque le mercredi, puis boulangerie le jeudi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camille, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
